--- a/latest/BoM/Positional/pedalboard-hw-bom.xlsx
+++ b/latest/BoM/Positional/pedalboard-hw-bom.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="583">
   <si>
     <t>Row</t>
   </si>
@@ -328,990 +328,996 @@
     <t>73.5802</t>
   </si>
   <si>
+    <t>8.3100</t>
+  </si>
+  <si>
+    <t>2.5900</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>CM4</t>
+  </si>
+  <si>
+    <t>pedalboard</t>
+  </si>
+  <si>
+    <t>CM1</t>
+  </si>
+  <si>
+    <t>Raspberry-Pi-4-Compute-Module</t>
+  </si>
+  <si>
+    <t>Pedalboard Library</t>
+  </si>
+  <si>
+    <t>https://www.hirose.com/en/product/document?clcode=&amp;productname=&amp;series=DF40&amp;documenttype=Catalog&amp;lang=en&amp;documentid=en_DF40_CAT</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/hirose-electric-co-ltd/DF40C-100DS-0-4V-51/1969476</t>
+  </si>
+  <si>
+    <t>/Audio</t>
+  </si>
+  <si>
+    <t>70.9944</t>
+  </si>
+  <si>
+    <t>67.4944</t>
+  </si>
+  <si>
+    <t>37.7000</t>
+  </si>
+  <si>
+    <t>50.7000</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Light emitting diode</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>LED R</t>
+  </si>
+  <si>
+    <t>LED_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>LED_SMD</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/harvatek-corporation/B1701URO-20D000114U1930/16671739</t>
+  </si>
+  <si>
+    <t>87.0844</t>
+  </si>
+  <si>
+    <t>53.2419</t>
+  </si>
+  <si>
+    <t>2.8500</t>
+  </si>
+  <si>
+    <t>1.4000</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>D2 D6</t>
+  </si>
+  <si>
+    <t>LED Y</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/harvatek-corporation/B1701NG-20D000314U1930/16671738</t>
+  </si>
+  <si>
+    <t>98.6944</t>
+  </si>
+  <si>
+    <t>73.3144</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1N4148</t>
+  </si>
+  <si>
+    <t>Diode</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SM4007</t>
+  </si>
+  <si>
+    <t>D_SOD-123F</t>
+  </si>
+  <si>
+    <t>Diode_SMD</t>
+  </si>
+  <si>
+    <t>https://www.mccsemi.com/pdf/Products/SM4001PL-SM4007PL(SOD-123FL).PDF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/micro-commercial-co/SM4007PL-TP/1793250</t>
+  </si>
+  <si>
+    <t>65.6560</t>
+  </si>
+  <si>
+    <t>89.0730</t>
+  </si>
+  <si>
+    <t>3.9000</t>
+  </si>
+  <si>
+    <t>1.1000</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Polyfuse</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Polyfuse 1.8A</t>
+  </si>
+  <si>
+    <t>Fuse_1812_4532Metric</t>
+  </si>
+  <si>
+    <t>Fuse</t>
+  </si>
+  <si>
+    <t>https://www.littelfuse.com/~/media/electronics/datasheets/resettable_ptcs/littelfuse_ptc_1812l_datasheet.pdf.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/littelfuse-inc/1812L150-24MR/2023969</t>
+  </si>
+  <si>
+    <t>148.0644</t>
+  </si>
+  <si>
+    <t>103.2844</t>
+  </si>
+  <si>
+    <t>5.4000</t>
+  </si>
+  <si>
+    <t>3.4000</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Conn_01x03_Pin</t>
+  </si>
+  <si>
+    <t>Connector</t>
+  </si>
+  <si>
+    <t>J28</t>
+  </si>
+  <si>
+    <t>JST PH 3</t>
+  </si>
+  <si>
+    <t>JST_PH_B3B-PH-SM4-TB_1x03-1MP_P2.00mm_Vertical</t>
+  </si>
+  <si>
+    <t>https://www.jst-mfg.com/product/pdf/eng/ePH.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/jst-sales-america-inc/B3B-PH-SM4-TB/926832</t>
+  </si>
+  <si>
+    <t>/LEDs</t>
+  </si>
+  <si>
+    <t>119.2944</t>
+  </si>
+  <si>
+    <t>78.1944</t>
+  </si>
+  <si>
+    <t>10.4000</t>
+  </si>
+  <si>
+    <t>6.5000</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Conn_01x04_Pin</t>
+  </si>
+  <si>
+    <t>J14</t>
+  </si>
+  <si>
+    <t>JST PH 4</t>
+  </si>
+  <si>
+    <t>JST_PH_B4B-PH-SM4-TB_1x04-1MP_P2.00mm_Vertical</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/jst-sales-america-inc./B4B-PH-SM4-TB/926833</t>
+  </si>
+  <si>
+    <t>128.2310</t>
+  </si>
+  <si>
+    <t>78.0252</t>
+  </si>
+  <si>
+    <t>12.4000</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>AudioJack3_SwitchTR</t>
+  </si>
+  <si>
+    <t>Connector_Audio</t>
+  </si>
+  <si>
+    <t>J1 J3</t>
+  </si>
+  <si>
+    <t>Jack 3.5mm</t>
+  </si>
+  <si>
+    <t>Jack_3.5mm_CUI_SJ1-3525N_Horizontal</t>
+  </si>
+  <si>
+    <t>https://www.cuidevices.com/product/resource/sj1-352xng.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/cui-devices/SJ1-3525NG/738690</t>
+  </si>
+  <si>
+    <t>71.9889</t>
+  </si>
+  <si>
+    <t>106.4944</t>
+  </si>
+  <si>
+    <t>THT</t>
+  </si>
+  <si>
+    <t>11.2000</t>
+  </si>
+  <si>
+    <t>6.7000</t>
+  </si>
+  <si>
+    <t>NMJ6HCD2</t>
+  </si>
+  <si>
+    <t>J5 J8 J18 J19 J20 J22</t>
+  </si>
+  <si>
+    <t>Jack 6.35mm</t>
+  </si>
+  <si>
+    <t>Jack_6.35mm_Horizontal</t>
+  </si>
+  <si>
+    <t>https://www.schurter.com/en/datasheet/typ_4833.2320.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/schurter-inc/4833-2320/2644235</t>
+  </si>
+  <si>
+    <t>pedalboard-hw(6)</t>
+  </si>
+  <si>
+    <t>157.6094</t>
+  </si>
+  <si>
+    <t>97.1944</t>
+  </si>
+  <si>
+    <t>0.0000</t>
+  </si>
+  <si>
+    <t>15.7000</t>
+  </si>
+  <si>
+    <t>19.2300</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Raspberry_Sound_Card</t>
+  </si>
+  <si>
+    <t>J27</t>
+  </si>
+  <si>
+    <t>Pedalboard Soundcard</t>
+  </si>
+  <si>
+    <t>Pedalboard_Soundcard</t>
+  </si>
+  <si>
+    <t>102.2444</t>
+  </si>
+  <si>
+    <t>62.6188</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
+    <t>41.4500</t>
+  </si>
+  <si>
+    <t>55.0150</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Screw_Terminal_01x02</t>
+  </si>
+  <si>
+    <t>J6</t>
+  </si>
+  <si>
+    <t>TerminalBlock_Phoenix_MKDS-1,5-2_1x02_P5.00mm_Horizontal</t>
+  </si>
+  <si>
+    <t>TerminalBlock_Phoenix</t>
+  </si>
+  <si>
+    <t>https://www.phoenixcontact.com/en-us/products/printed-circuit-board-terminal-mkds-15-2-1715022?type=pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/phoenix-contact/1715022/260626</t>
+  </si>
+  <si>
+    <t>157.6316</t>
+  </si>
+  <si>
+    <t>102.7958</t>
+  </si>
+  <si>
+    <t>7.6000</t>
+  </si>
+  <si>
+    <t>2.6000</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>USB Type A connector</t>
+  </si>
+  <si>
+    <t>USB_A</t>
+  </si>
+  <si>
+    <t>J10</t>
+  </si>
+  <si>
+    <t>USB_A_Molex_67643_Horizontal</t>
+  </si>
+  <si>
+    <t>Connector_USB</t>
+  </si>
+  <si>
+    <t>https://www.molex.com/en-us/products/part-detail/676433910?display=pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/molex/0676433910/3598521</t>
+  </si>
+  <si>
+    <t>35.0744</t>
+  </si>
+  <si>
+    <t>99.2444</t>
+  </si>
+  <si>
+    <t>16.1400</t>
+  </si>
+  <si>
+    <t>5.0100</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>USB mini/micro connector</t>
+  </si>
+  <si>
+    <t>USB_OTG</t>
+  </si>
+  <si>
+    <t>J9</t>
+  </si>
+  <si>
+    <t>USB_Micro-B_Amphenol_10103594-0001LF_Horizontal</t>
+  </si>
+  <si>
+    <t>https://cdn.amphenol-cs.com/media/wysiwyg/files/drawing/10103594.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/amphenol-cs-fci/10103594-0001LF/2350351</t>
+  </si>
+  <si>
+    <t>2.6644</t>
+  </si>
+  <si>
+    <t>74.4944</t>
+  </si>
+  <si>
+    <t>7.7750</t>
+  </si>
+  <si>
+    <t>5.2700</t>
+  </si>
+  <si>
+    <t>L_Ferrite</t>
+  </si>
+  <si>
+    <t>L1 L2 L3 L4</t>
+  </si>
+  <si>
+    <t>120_100MHz</t>
+  </si>
+  <si>
+    <t>L_0603_1608Metric</t>
+  </si>
+  <si>
+    <t>Inductor_SMD</t>
+  </si>
+  <si>
+    <t>https://www.murata.com/products/productdata/8796738650142/ENFA0003.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/murata-electronics/BLM18KG121TN1D/1982762</t>
+  </si>
+  <si>
+    <t>63.0160</t>
+  </si>
+  <si>
+    <t>87.5730</t>
+  </si>
+  <si>
+    <t>2.4500</t>
+  </si>
+  <si>
+    <t>0.9500</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>L5</t>
+  </si>
+  <si>
+    <t>SRN6045TA-3R3Y</t>
+  </si>
+  <si>
+    <t>L_Bourns_SRN6045TA</t>
+  </si>
+  <si>
+    <t>https://www.bourns.com/docs/Product-Datasheets/SRN6045TA.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/bourns-inc/SRN6045TA-3R3Y/6155103</t>
+  </si>
+  <si>
+    <t>146.8944</t>
+  </si>
+  <si>
+    <t>80.8544</t>
+  </si>
+  <si>
+    <t>5.1000</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>FDS4435BZ</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>SO08-E3</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pdf/datasheet/fds4435bz_f085-d.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/onsemi/FDS4435BZ/1305763</t>
+  </si>
+  <si>
+    <t>141.8544</t>
+  </si>
+  <si>
+    <t>102.8344</t>
+  </si>
+  <si>
+    <t>4.4150</t>
+  </si>
+  <si>
+    <t>7.4000</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Resistor, small symbol</t>
+  </si>
+  <si>
+    <t>R_Small</t>
+  </si>
+  <si>
+    <t>R5 R13</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>R_0805_2012Metric</t>
+  </si>
+  <si>
+    <t>Resistor_SMD</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RNCP0805FTD10R0/2240197</t>
+  </si>
+  <si>
+    <t>75.2034</t>
+  </si>
+  <si>
+    <t>86.7030</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R6 R10</t>
+  </si>
+  <si>
+    <t>27R</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT27R0/1712920</t>
+  </si>
+  <si>
+    <t>81.3944</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>33R</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT33R0/1760586</t>
+  </si>
+  <si>
+    <t>88.6030</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R3 R7 R20</t>
+  </si>
+  <si>
+    <t>220R</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT220R/1760238</t>
+  </si>
+  <si>
+    <t>pedalboard-hw(3)</t>
+  </si>
+  <si>
+    <t>63.5410</t>
+  </si>
+  <si>
+    <t>89.9980</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R1 R2 R8 R11 R16</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RNCP0805FTD1K00/2240229</t>
+  </si>
+  <si>
+    <t>pedalboard-hw(5)</t>
+  </si>
+  <si>
+    <t>133.1920</t>
+  </si>
+  <si>
+    <t>107.2606</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R15 R17 R21 R22 R23</t>
+  </si>
+  <si>
+    <t>2K2</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT2K20/1760345</t>
+  </si>
+  <si>
+    <t>137.8244</t>
+  </si>
+  <si>
+    <t>87.2244</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>R18 R19</t>
+  </si>
+  <si>
+    <t>3K9</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT3K90/1760599</t>
+  </si>
+  <si>
+    <t>131.8444</t>
+  </si>
+  <si>
+    <t>85.7444</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>R12 R24</t>
+  </si>
+  <si>
+    <t>12K</t>
+  </si>
+  <si>
+    <t>135.9044</t>
+  </si>
+  <si>
+    <t>83.8644</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>20K</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT20K0/1760314</t>
+  </si>
+  <si>
+    <t>140.6644</t>
+  </si>
+  <si>
+    <t>81.1944</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R25 R26 R27 R28 R29</t>
+  </si>
+  <si>
+    <t>36K</t>
+  </si>
+  <si>
+    <t>32.3744</t>
+  </si>
+  <si>
+    <t>78.3300</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>RotaryEncoder_Switch</t>
+  </si>
+  <si>
+    <t>SW1 SW2</t>
+  </si>
+  <si>
+    <t>24P/R 24mm</t>
+  </si>
+  <si>
+    <t>RotaryEncoder_Alps_EC11E-Switch_Vertical_H20mm_CircularMountingHoles</t>
+  </si>
+  <si>
+    <t>https://www.bourns.com/docs/Product-Datasheets/PEC11R.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/bourns-inc/PEC11R-4225F-S0024/4499659</t>
+  </si>
+  <si>
+    <t>42.2444</t>
+  </si>
+  <si>
+    <t>99.4944</t>
+  </si>
+  <si>
+    <t>16.5000</t>
+  </si>
+  <si>
+    <t>14.4000</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>SW_Omron_B3FS</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>SW5 SW6 SW7 SW8 SW9 SW10</t>
+  </si>
+  <si>
+    <t>Tactile Button</t>
+  </si>
+  <si>
+    <t>SW_PUSH-12mm_Wuerth</t>
+  </si>
+  <si>
+    <t>https://www.we-online.com/components/products/datasheet/430172043816.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/w%C3%BCrth-elektronik/430162043826/9950802</t>
+  </si>
+  <si>
+    <t>11.9944</t>
+  </si>
+  <si>
+    <t>63.9944</t>
+  </si>
+  <si>
+    <t>16.0000</t>
+  </si>
+  <si>
+    <t>6.8000</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>74AHCT1G32SE-7</t>
+  </si>
+  <si>
+    <t>U1 U7</t>
+  </si>
+  <si>
+    <t>SOT-353_SC-70-5</t>
+  </si>
+  <si>
+    <t>Package_TO_SOT_SMD</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/74AHCT1G32.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/74AHCT1G32SE-7/2711987</t>
+  </si>
+  <si>
+    <t>121.7444</t>
+  </si>
+  <si>
+    <t>87.4944</t>
+  </si>
+  <si>
+    <t>2.5500</t>
+  </si>
+  <si>
+    <t>1.7000</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>AP2553W6</t>
+  </si>
+  <si>
+    <t>U10</t>
+  </si>
+  <si>
+    <t>SOT-23-6</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AP255x.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/en/products/detail/AP2553W6-7/AP2553W6-7DICT-ND/3882112</t>
+  </si>
+  <si>
+    <t>55.0870</t>
+  </si>
+  <si>
+    <t>79.1174</t>
+  </si>
+  <si>
+    <t>3.6000</t>
+  </si>
+  <si>
+    <t>2.5000</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>AP64351</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>AP64501SP-13</t>
+  </si>
+  <si>
+    <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.71x3.4mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AP64501.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AP64501SP-13/10419715</t>
+  </si>
+  <si>
+    <t>141.5144</t>
+  </si>
+  <si>
+    <t>88.5944</t>
+  </si>
+  <si>
+    <t>6.9000</t>
+  </si>
+  <si>
+    <t>4.9000</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>I2C Serial EEPROM, 1Kb (128x8) with Unique Serial Number, SOT-23-5</t>
+  </si>
+  <si>
+    <t>AT24CS01-STUM</t>
+  </si>
+  <si>
+    <t>Memory_EEPROM</t>
+  </si>
+  <si>
+    <t>U12</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/Atmel-8815-SEEPROM-AT24CS01-02-Datasheet.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/microchip-technology/AT24CS01-STUM-T/3973063</t>
+  </si>
+  <si>
+    <t>127.9944</t>
+  </si>
+  <si>
+    <t>86.4944</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>Low-Power, Two-Port, High-Speed, USB2.0 (480Mbps) or UART Switch, MSOP-10</t>
+  </si>
+  <si>
+    <t>FSUSB42MUX</t>
+  </si>
+  <si>
+    <t>Interface_USB</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <t>TSSOP-10_3x3mm_P0.5mm</t>
+  </si>
+  <si>
+    <t>Package_SO</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pub/Collateral/FSUSB42-D.PDF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/onsemi/FSUSB42MUX/2036916</t>
+  </si>
+  <si>
+    <t>38.1144</t>
+  </si>
+  <si>
+    <t>73.8844</t>
+  </si>
+  <si>
+    <t>2.2500</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>NCP1117-3.3_SOT223</t>
+  </si>
+  <si>
+    <t>Regulator_Linear</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>SOT-223-3_TabPin2</t>
+  </si>
+  <si>
+    <t>https://www.diodes.com/assets/Datasheets/AZ1117I.pdf</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AZ1117IH-3-3TRG1/5699672</t>
+  </si>
+  <si>
+    <t>104.8844</t>
+  </si>
+  <si>
+    <t>76.9444</t>
+  </si>
+  <si>
     <t>8.3000</t>
   </si>
   <si>
-    <t>2.5500</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>CM4</t>
-  </si>
-  <si>
-    <t>pedalboard</t>
-  </si>
-  <si>
-    <t>CM1</t>
-  </si>
-  <si>
-    <t>Raspberry-Pi-4-Compute-Module</t>
-  </si>
-  <si>
-    <t>Pedalboard Library</t>
-  </si>
-  <si>
-    <t>https://www.hirose.com/en/product/document?clcode=&amp;productname=&amp;series=DF40&amp;documenttype=Catalog&amp;lang=en&amp;documentid=en_DF40_CAT</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/hirose-electric-co-ltd/DF40C-100DS-0-4V-51/1969476</t>
-  </si>
-  <si>
-    <t>/Audio</t>
-  </si>
-  <si>
-    <t>-18.0056</t>
-  </si>
-  <si>
-    <t>130.9944</t>
-  </si>
-  <si>
-    <t>0.0000</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>LED R</t>
-  </si>
-  <si>
-    <t>LED_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>LED_SMD</t>
-  </si>
-  <si>
-    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/3739/B1701URO-20D000114U1930.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/harvatek-corporation/B1701URO-20D000114U1930/16671739</t>
-  </si>
-  <si>
-    <t>87.0844</t>
-  </si>
-  <si>
-    <t>53.2419</t>
-  </si>
-  <si>
-    <t>2.8500</t>
-  </si>
-  <si>
-    <t>1.4000</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>D2 D6</t>
-  </si>
-  <si>
-    <t>LED Y</t>
-  </si>
-  <si>
-    <t>https://mm.digikey.com/Volume0/opasdata/d220001/medias/docus/3804/B1701NG--20D000314U1930.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/harvatek-corporation/B1701NG-20D000314U1930/16671738</t>
-  </si>
-  <si>
-    <t>98.6944</t>
-  </si>
-  <si>
-    <t>73.3144</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>1N4148</t>
-  </si>
-  <si>
-    <t>Diode</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>SM4007</t>
-  </si>
-  <si>
-    <t>D_SOD-123F</t>
-  </si>
-  <si>
-    <t>Diode_SMD</t>
-  </si>
-  <si>
-    <t>https://www.mccsemi.com/pdf/Products/SM4001PL-SM4007PL(SOD-123FL).PDF</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/micro-commercial-co/SM4007PL-TP/1793250</t>
-  </si>
-  <si>
-    <t>65.6560</t>
-  </si>
-  <si>
-    <t>89.0730</t>
-  </si>
-  <si>
-    <t>3.9000</t>
-  </si>
-  <si>
-    <t>1.1000</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>Polyfuse</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Polyfuse 1.8A</t>
-  </si>
-  <si>
-    <t>Fuse_1812_4532Metric</t>
-  </si>
-  <si>
-    <t>Fuse</t>
-  </si>
-  <si>
-    <t>https://www.littelfuse.com/~/media/electronics/datasheets/resettable_ptcs/littelfuse_ptc_1812l_datasheet.pdf.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/littelfuse-inc/1812L150-24MR/2023969</t>
-  </si>
-  <si>
-    <t>148.0644</t>
-  </si>
-  <si>
-    <t>103.2844</t>
-  </si>
-  <si>
-    <t>5.4000</t>
-  </si>
-  <si>
-    <t>3.4000</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>Conn_01x03_Pin</t>
-  </si>
-  <si>
-    <t>Connector</t>
-  </si>
-  <si>
-    <t>J28</t>
-  </si>
-  <si>
-    <t>JST PH 3</t>
-  </si>
-  <si>
-    <t>JST_PH_B3B-PH-SM4-TB_1x03-1MP_P2.00mm_Vertical</t>
-  </si>
-  <si>
-    <t>https://www.jst-mfg.com/product/pdf/eng/ePH.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/jst-sales-america-inc/B3B-PH-SM4-TB/926832</t>
-  </si>
-  <si>
-    <t>/LEDs</t>
-  </si>
-  <si>
-    <t>119.2944</t>
-  </si>
-  <si>
-    <t>78.1944</t>
-  </si>
-  <si>
-    <t>10.4000</t>
-  </si>
-  <si>
-    <t>6.5000</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>Conn_01x04_Pin</t>
-  </si>
-  <si>
-    <t>J14</t>
-  </si>
-  <si>
-    <t>JST PH 4</t>
-  </si>
-  <si>
-    <t>JST_PH_B4B-PH-SM4-TB_1x04-1MP_P2.00mm_Vertical</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/jst-sales-america-inc./B4B-PH-SM4-TB/926833</t>
-  </si>
-  <si>
-    <t>128.2310</t>
-  </si>
-  <si>
-    <t>78.0252</t>
-  </si>
-  <si>
-    <t>12.4000</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>AudioJack3_SwitchTR</t>
-  </si>
-  <si>
-    <t>Connector_Audio</t>
-  </si>
-  <si>
-    <t>J1 J3</t>
-  </si>
-  <si>
-    <t>Jack 3.5mm</t>
-  </si>
-  <si>
-    <t>Jack_3.5mm_CUI_SJ1-3525N_Horizontal</t>
-  </si>
-  <si>
-    <t>https://www.cuidevices.com/product/resource/sj1-352xng.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/cui-devices/SJ1-3525NG/738690</t>
-  </si>
-  <si>
-    <t>71.9889</t>
-  </si>
-  <si>
-    <t>106.4944</t>
-  </si>
-  <si>
-    <t>THT</t>
-  </si>
-  <si>
-    <t>11.2000</t>
-  </si>
-  <si>
-    <t>6.7000</t>
-  </si>
-  <si>
-    <t>NMJ6HCD2</t>
-  </si>
-  <si>
-    <t>J5 J8 J18 J19 J20 J22</t>
-  </si>
-  <si>
-    <t>Jack 6.35mm</t>
-  </si>
-  <si>
-    <t>Jack_6.35mm_Horizontal</t>
-  </si>
-  <si>
-    <t>https://www.schurter.com/en/datasheet/typ_4833.2320.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/schurter-inc/4833-2320/2644235</t>
-  </si>
-  <si>
-    <t>pedalboard-hw(6)</t>
-  </si>
-  <si>
-    <t>157.6094</t>
-  </si>
-  <si>
-    <t>97.1944</t>
-  </si>
-  <si>
-    <t>15.7000</t>
-  </si>
-  <si>
-    <t>19.2300</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>Raspberry_Sound_Card</t>
-  </si>
-  <si>
-    <t>J27</t>
-  </si>
-  <si>
-    <t>Pedalboard Soundcard</t>
-  </si>
-  <si>
-    <t>Pedalboard_Soundcard</t>
-  </si>
-  <si>
-    <t>~</t>
-  </si>
-  <si>
-    <t>102.2444</t>
-  </si>
-  <si>
-    <t>62.6188</t>
-  </si>
-  <si>
-    <t>bottom</t>
-  </si>
-  <si>
-    <t>41.4500</t>
-  </si>
-  <si>
-    <t>55.0150</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>Screw_Terminal_01x02</t>
-  </si>
-  <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>TerminalBlock_Phoenix_MKDS-1,5-2_1x02_P5.00mm_Horizontal</t>
-  </si>
-  <si>
-    <t>TerminalBlock_Phoenix</t>
-  </si>
-  <si>
-    <t>https://www.phoenixcontact.com/en-us/products/printed-circuit-board-terminal-mkds-15-2-1715022?type=pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/phoenix-contact/1715022/260626</t>
-  </si>
-  <si>
-    <t>157.6316</t>
-  </si>
-  <si>
-    <t>102.7958</t>
-  </si>
-  <si>
-    <t>7.6000</t>
-  </si>
-  <si>
-    <t>2.6000</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>USB Type A connector</t>
-  </si>
-  <si>
-    <t>USB_A</t>
-  </si>
-  <si>
-    <t>J10</t>
-  </si>
-  <si>
-    <t>USB_A_Molex_67643_Horizontal</t>
-  </si>
-  <si>
-    <t>Connector_USB</t>
-  </si>
-  <si>
-    <t>https://www.molex.com/en-us/products/part-detail/676433910?display=pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/molex/0676433910/3598521</t>
-  </si>
-  <si>
-    <t>35.0744</t>
-  </si>
-  <si>
-    <t>99.2444</t>
-  </si>
-  <si>
-    <t>16.1400</t>
-  </si>
-  <si>
-    <t>5.0100</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>USB mini/micro connector</t>
-  </si>
-  <si>
-    <t>USB_OTG</t>
-  </si>
-  <si>
-    <t>J9</t>
-  </si>
-  <si>
-    <t>USB_Micro-B_Amphenol_10103594-0001LF_Horizontal</t>
-  </si>
-  <si>
-    <t>https://cdn.amphenol-cs.com/media/wysiwyg/files/drawing/10103594.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/amphenol-cs-fci/10103594-0001LF/2350351</t>
-  </si>
-  <si>
-    <t>2.6644</t>
-  </si>
-  <si>
-    <t>74.4944</t>
-  </si>
-  <si>
-    <t>7.7750</t>
-  </si>
-  <si>
-    <t>5.2700</t>
-  </si>
-  <si>
-    <t>L_Ferrite</t>
-  </si>
-  <si>
-    <t>L1 L2 L3 L4</t>
-  </si>
-  <si>
-    <t>120_100MHz</t>
-  </si>
-  <si>
-    <t>L_0603_1608Metric</t>
-  </si>
-  <si>
-    <t>Inductor_SMD</t>
-  </si>
-  <si>
-    <t>https://www.murata.com/products/productdata/8796738650142/ENFA0003.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/murata-electronics/BLM18KG121TN1D/1982762</t>
-  </si>
-  <si>
-    <t>63.0160</t>
-  </si>
-  <si>
-    <t>87.5730</t>
-  </si>
-  <si>
-    <t>2.4500</t>
-  </si>
-  <si>
-    <t>0.9500</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>L5</t>
-  </si>
-  <si>
-    <t>SRN6045TA-3R3Y</t>
-  </si>
-  <si>
-    <t>L_Bourns_SRN6045TA</t>
-  </si>
-  <si>
-    <t>https://www.bourns.com/docs/Product-Datasheets/SRN6045TA.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/bourns-inc/SRN6045TA-3R3Y/6155103</t>
-  </si>
-  <si>
-    <t>146.8944</t>
-  </si>
-  <si>
-    <t>80.8544</t>
-  </si>
-  <si>
-    <t>5.1000</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>FDS4435BZ</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>SO08-E3</t>
-  </si>
-  <si>
-    <t>https://www.onsemi.com/pdf/datasheet/fds4435bz_f085-d.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/onsemi/FDS4435BZ/1305763</t>
-  </si>
-  <si>
-    <t>141.8544</t>
-  </si>
-  <si>
-    <t>102.8344</t>
-  </si>
-  <si>
-    <t>4.4150</t>
-  </si>
-  <si>
-    <t>7.4000</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>R_Small</t>
-  </si>
-  <si>
-    <t>R5 R13</t>
-  </si>
-  <si>
-    <t>10R</t>
-  </si>
-  <si>
-    <t>R_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>Resistor_SMD</t>
-  </si>
-  <si>
-    <t>https://www.seielect.com/catalog/sei-rncp.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RNCP0805FTD10R0/2240197</t>
-  </si>
-  <si>
-    <t>75.2034</t>
-  </si>
-  <si>
-    <t>86.7030</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>R6 R10</t>
-  </si>
-  <si>
-    <t>27R</t>
-  </si>
-  <si>
-    <t>https://www.seielect.com/catalog/sei-rmcf_rmcp.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT27R0/1712920</t>
-  </si>
-  <si>
-    <t>81.3944</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>33R</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT33R0/1760586</t>
-  </si>
-  <si>
-    <t>88.6030</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R3 R7 R20</t>
-  </si>
-  <si>
-    <t>220R</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT220R/1760238</t>
-  </si>
-  <si>
-    <t>pedalboard-hw(3)</t>
-  </si>
-  <si>
-    <t>63.5410</t>
-  </si>
-  <si>
-    <t>89.9980</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R1 R2 R8 R11 R16</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RNCP0805FTD1K00/2240229</t>
-  </si>
-  <si>
-    <t>pedalboard-hw(5)</t>
-  </si>
-  <si>
-    <t>133.1920</t>
-  </si>
-  <si>
-    <t>107.2606</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R15 R17 R21 R22 R23</t>
-  </si>
-  <si>
-    <t>2K2</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT2K20/1760345</t>
-  </si>
-  <si>
-    <t>137.8244</t>
-  </si>
-  <si>
-    <t>87.2244</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>R18 R19</t>
-  </si>
-  <si>
-    <t>3K9</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT3K90/1760599</t>
-  </si>
-  <si>
-    <t>131.8444</t>
-  </si>
-  <si>
-    <t>85.7444</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>R12 R24</t>
-  </si>
-  <si>
-    <t>12K</t>
-  </si>
-  <si>
-    <t>135.9044</t>
-  </si>
-  <si>
-    <t>83.8644</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R14</t>
-  </si>
-  <si>
-    <t>20K</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/stackpole-electronics-inc/RMCF0805FT20K0/1760314</t>
-  </si>
-  <si>
-    <t>140.6644</t>
-  </si>
-  <si>
-    <t>81.1944</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R25 R26 R27 R28 R29</t>
-  </si>
-  <si>
-    <t>36K</t>
-  </si>
-  <si>
-    <t>32.3744</t>
-  </si>
-  <si>
-    <t>78.3300</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>RotaryEncoder_Switch</t>
-  </si>
-  <si>
-    <t>SW1 SW2</t>
-  </si>
-  <si>
-    <t>24P/R 24mm</t>
-  </si>
-  <si>
-    <t>RotaryEncoder_Alps_EC11E-Switch_Vertical_H20mm_CircularMountingHoles</t>
-  </si>
-  <si>
-    <t>https://www.bourns.com/docs/Product-Datasheets/PEC11R.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/bourns-inc/PEC11R-4225F-S0024/4499659</t>
-  </si>
-  <si>
-    <t>42.2444</t>
-  </si>
-  <si>
-    <t>99.4944</t>
-  </si>
-  <si>
-    <t>16.5000</t>
-  </si>
-  <si>
-    <t>14.4000</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>SW_Omron_B3FS</t>
-  </si>
-  <si>
-    <t>Switch</t>
-  </si>
-  <si>
-    <t>SW5 SW6 SW7 SW8 SW9 SW10</t>
-  </si>
-  <si>
-    <t>Tactile Button</t>
-  </si>
-  <si>
-    <t>SW_PUSH-12mm_Wuerth</t>
-  </si>
-  <si>
-    <t>https://www.we-online.com/components/products/datasheet/430172043816.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/w%C3%BCrth-elektronik/430162043826/9950802</t>
-  </si>
-  <si>
-    <t>11.9944</t>
-  </si>
-  <si>
-    <t>63.9944</t>
-  </si>
-  <si>
-    <t>16.0000</t>
-  </si>
-  <si>
-    <t>6.8000</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>74AHCT1G32SE-7</t>
-  </si>
-  <si>
-    <t>U1 U7</t>
-  </si>
-  <si>
-    <t>SOT-353_SC-70-5</t>
-  </si>
-  <si>
-    <t>Package_TO_SOT_SMD</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/74AHCT1G32.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/74AHCT1G32SE-7/2711987</t>
-  </si>
-  <si>
-    <t>121.7444</t>
-  </si>
-  <si>
-    <t>87.4944</t>
-  </si>
-  <si>
-    <t>1.7000</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>AP2553W6</t>
-  </si>
-  <si>
-    <t>U10</t>
-  </si>
-  <si>
-    <t>SOT-23-6</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AP255x.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/en/products/detail/AP2553W6-7/AP2553W6-7DICT-ND/3882112</t>
-  </si>
-  <si>
-    <t>55.0870</t>
-  </si>
-  <si>
-    <t>79.1174</t>
-  </si>
-  <si>
-    <t>3.6000</t>
-  </si>
-  <si>
-    <t>2.5000</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>AP64351</t>
-  </si>
-  <si>
-    <t>U6</t>
-  </si>
-  <si>
-    <t>AP64501SP-13</t>
-  </si>
-  <si>
-    <t>SOIC-8-1EP_3.9x4.9mm_P1.27mm_EP2.95x4.9mm_Mask2.71x3.4mm_ThermalVias</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AP64501.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AP64501SP-13/10419715</t>
-  </si>
-  <si>
-    <t>141.5144</t>
-  </si>
-  <si>
-    <t>88.5944</t>
-  </si>
-  <si>
-    <t>6.9000</t>
-  </si>
-  <si>
-    <t>4.9000</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>I2C Serial EEPROM, 1Kb (128x8) with Unique Serial Number, SOT-23-5</t>
-  </si>
-  <si>
-    <t>AT24CS01-STUM</t>
-  </si>
-  <si>
-    <t>Memory_EEPROM</t>
-  </si>
-  <si>
-    <t>U12</t>
-  </si>
-  <si>
-    <t>SOT-23-5</t>
-  </si>
-  <si>
-    <t>http://ww1.microchip.com/downloads/en/DeviceDoc/Atmel-8815-SEEPROM-AT24CS01-02-Datasheet.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/microchip-technology/AT24CS01-STUM-T/3973063</t>
-  </si>
-  <si>
-    <t>127.9944</t>
-  </si>
-  <si>
-    <t>86.4944</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Low-Power, Two-Port, High-Speed, USB2.0 (480Mbps) or UART Switch, MSOP-10</t>
-  </si>
-  <si>
-    <t>FSUSB42MUX</t>
-  </si>
-  <si>
-    <t>Interface_USB</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>TSSOP-10_3x3mm_P0.5mm</t>
-  </si>
-  <si>
-    <t>Package_SO</t>
-  </si>
-  <si>
-    <t>https://www.onsemi.com/pub/Collateral/FSUSB42-D.PDF</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/onsemi/FSUSB42MUX/2036916</t>
-  </si>
-  <si>
-    <t>38.1144</t>
-  </si>
-  <si>
-    <t>73.8844</t>
-  </si>
-  <si>
-    <t>2.2500</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>NCP1117-3.3_SOT223</t>
-  </si>
-  <si>
-    <t>Regulator_Linear</t>
-  </si>
-  <si>
-    <t>U5</t>
-  </si>
-  <si>
-    <t>SOT-223-3_TabPin2</t>
-  </si>
-  <si>
-    <t>https://www.diodes.com/assets/Datasheets/AZ1117I.pdf</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ch/de/products/detail/diodes-incorporated/AZ1117IH-3-3TRG1/5699672</t>
-  </si>
-  <si>
-    <t>104.8844</t>
-  </si>
-  <si>
-    <t>76.9444</t>
-  </si>
-  <si>
     <t>6.1000</t>
   </si>
   <si>
@@ -1573,7 +1579,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>8.0.6+1</t>
+    <t>9.0.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -1582,13 +1588,13 @@
     <t>Component Count:</t>
   </si>
   <si>
-    <t>138 (117 SMD/ 20 THT)</t>
+    <t>138 (118 SMD/ 20 THT)</t>
   </si>
   <si>
     <t>Fitted Components:</t>
   </si>
   <si>
-    <t>128 (114 SMD/ 13 THT)</t>
+    <t>128 (115 SMD/ 13 THT)</t>
   </si>
   <si>
     <t>Number of PCBs:</t>
@@ -1631,6 +1637,9 @@
   </si>
   <si>
     <t>7.9000</t>
+  </si>
+  <si>
+    <t>5-pin DIN connector (5-pin DIN-5 stereo)</t>
   </si>
   <si>
     <t>DIN-5_180degree</t>
@@ -1929,10 +1938,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>1071975</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>297815</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1464384</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1959,7 +1968,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9396825" cy="5079365"/>
+          <a:ext cx="2378784" cy="1285829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1981,10 +1990,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>910050</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>107315</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1464384</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2011,7 +2020,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9396825" cy="5079365"/>
+          <a:ext cx="2378784" cy="1285829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2338,7 +2347,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2363,13 +2372,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F2" s="3">
         <v>55</v>
@@ -2377,41 +2386,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -2419,13 +2428,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F6" s="3">
         <v>128</v>
@@ -3123,7 +3132,7 @@
         <v>114</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="S17" s="7" t="s">
         <v>40</v>
@@ -3138,33 +3147,33 @@
         <v>115</v>
       </c>
       <c r="W17" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="30" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>24</v>
+        <v>117</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>23</v>
@@ -3175,11 +3184,11 @@
       <c r="K18" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="11" t="s">
-        <v>122</v>
+      <c r="L18" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N18" s="11" t="s">
         <v>112</v>
@@ -3188,10 +3197,10 @@
         <v>66</v>
       </c>
       <c r="P18" s="11" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="Q18" s="11" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="R18" s="11" t="s">
         <v>77</v>
@@ -3206,36 +3215,36 @@
         <v>42</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="30" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>24</v>
+        <v>130</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>118</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>31</v>
@@ -3246,11 +3255,11 @@
       <c r="K19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L19" s="7" t="s">
-        <v>131</v>
+      <c r="L19" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>35</v>
@@ -3259,10 +3268,10 @@
         <v>36</v>
       </c>
       <c r="P19" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R19" s="7" t="s">
         <v>39</v>
@@ -3277,36 +3286,36 @@
         <v>42</v>
       </c>
       <c r="V19" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W19" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="30" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>23</v>
@@ -3318,10 +3327,10 @@
         <v>32</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M20" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="11" t="s">
         <v>35</v>
@@ -3330,10 +3339,10 @@
         <v>66</v>
       </c>
       <c r="P20" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q20" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="R20" s="11" t="s">
         <v>77</v>
@@ -3348,36 +3357,36 @@
         <v>42</v>
       </c>
       <c r="V20" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="W20" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="30" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>23</v>
@@ -3389,10 +3398,10 @@
         <v>32</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N21" s="7" t="s">
         <v>58</v>
@@ -3401,10 +3410,10 @@
         <v>66</v>
       </c>
       <c r="P21" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R21" s="7" t="s">
         <v>39</v>
@@ -3419,33 +3428,33 @@
         <v>42</v>
       </c>
       <c r="V21" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W21" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="30" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H22" s="11" t="s">
         <v>109</v>
@@ -3460,22 +3469,22 @@
         <v>32</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M22" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O22" s="9" t="s">
         <v>66</v>
       </c>
       <c r="P22" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q22" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="R22" s="11" t="s">
         <v>51</v>
@@ -3490,33 +3499,33 @@
         <v>42</v>
       </c>
       <c r="V22" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="W22" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="30" customHeight="1">
       <c r="A23" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>109</v>
@@ -3531,10 +3540,10 @@
         <v>32</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>35</v>
@@ -3543,10 +3552,10 @@
         <v>66</v>
       </c>
       <c r="P23" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R23" s="7" t="s">
         <v>51</v>
@@ -3561,33 +3570,33 @@
         <v>42</v>
       </c>
       <c r="V23" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="W23" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="30" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>109</v>
@@ -3602,10 +3611,10 @@
         <v>32</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M24" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N24" s="11" t="s">
         <v>35</v>
@@ -3614,10 +3623,10 @@
         <v>36</v>
       </c>
       <c r="P24" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q24" s="11" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R24" s="11" t="s">
         <v>39</v>
@@ -3626,16 +3635,16 @@
         <v>40</v>
       </c>
       <c r="T24" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U24" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V24" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="W24" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="30" customHeight="1">
@@ -3646,19 +3655,19 @@
         <v>24</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>109</v>
@@ -3673,63 +3682,63 @@
         <v>32</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>35</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P25" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S25" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T25" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U25" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V25" s="7" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="W25" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:23">
       <c r="A26" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B26" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H26" s="11" t="s">
         <v>109</v>
@@ -3744,7 +3753,7 @@
         <v>32</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="M26" s="10" t="s">
         <v>24</v>
@@ -3756,54 +3765,54 @@
         <v>66</v>
       </c>
       <c r="P26" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q26" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="R26" s="11" t="s">
         <v>39</v>
       </c>
       <c r="S26" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T26" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U26" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="30" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E27" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>218</v>
-      </c>
       <c r="G27" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>23</v>
@@ -3815,10 +3824,10 @@
         <v>32</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N27" s="7" t="s">
         <v>58</v>
@@ -3827,10 +3836,10 @@
         <v>66</v>
       </c>
       <c r="P27" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>51</v>
@@ -3839,42 +3848,42 @@
         <v>40</v>
       </c>
       <c r="T27" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U27" s="7" t="s">
         <v>42</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="W27" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="30" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F28" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="F28" s="11" t="s">
-        <v>230</v>
-      </c>
       <c r="G28" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>23</v>
@@ -3886,10 +3895,10 @@
         <v>32</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M28" s="12" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N28" s="11" t="s">
         <v>48</v>
@@ -3898,10 +3907,10 @@
         <v>66</v>
       </c>
       <c r="P28" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q28" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R28" s="11" t="s">
         <v>39</v>
@@ -3910,39 +3919,39 @@
         <v>40</v>
       </c>
       <c r="T28" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U28" s="11" t="s">
         <v>42</v>
       </c>
       <c r="V28" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="W28" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="30" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E29" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="F29" s="7" t="s">
-        <v>242</v>
-      </c>
       <c r="G29" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>109</v>
@@ -3957,10 +3966,10 @@
         <v>32</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>48</v>
@@ -3969,10 +3978,10 @@
         <v>66</v>
       </c>
       <c r="P29" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R29" s="7" t="s">
         <v>77</v>
@@ -3987,10 +3996,10 @@
         <v>42</v>
       </c>
       <c r="V29" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="W29" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="30" customHeight="1">
@@ -4001,22 +4010,22 @@
         <v>24</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>55</v>
@@ -4028,10 +4037,10 @@
         <v>32</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M30" s="12" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N30" s="11" t="s">
         <v>35</v>
@@ -4040,13 +4049,13 @@
         <v>59</v>
       </c>
       <c r="P30" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q30" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R30" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S30" s="11" t="s">
         <v>40</v>
@@ -4058,36 +4067,36 @@
         <v>42</v>
       </c>
       <c r="V30" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="30" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>23</v>
@@ -4099,10 +4108,10 @@
         <v>32</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N31" s="7" t="s">
         <v>58</v>
@@ -4111,10 +4120,10 @@
         <v>66</v>
       </c>
       <c r="P31" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="R31" s="7" t="s">
         <v>77</v>
@@ -4129,33 +4138,33 @@
         <v>42</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="W31" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="30" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>273</v>
-      </c>
       <c r="G32" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>109</v>
@@ -4170,10 +4179,10 @@
         <v>32</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M32" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N32" s="11" t="s">
         <v>58</v>
@@ -4182,13 +4191,13 @@
         <v>66</v>
       </c>
       <c r="P32" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q32" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="R32" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S32" s="11" t="s">
         <v>40</v>
@@ -4200,36 +4209,36 @@
         <v>42</v>
       </c>
       <c r="V32" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:23" ht="30" customHeight="1">
       <c r="A33" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>24</v>
+        <v>283</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>31</v>
@@ -4240,11 +4249,11 @@
       <c r="K33" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>288</v>
+      <c r="L33" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>35</v>
@@ -4253,13 +4262,13 @@
         <v>36</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S33" s="7" t="s">
         <v>40</v>
@@ -4271,36 +4280,36 @@
         <v>42</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W33" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:23" ht="30" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>24</v>
+        <v>293</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>31</v>
@@ -4311,8 +4320,8 @@
       <c r="K34" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L34" s="11" t="s">
-        <v>295</v>
+      <c r="L34" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M34" s="12" t="s">
         <v>296</v>
@@ -4330,7 +4339,7 @@
         <v>50</v>
       </c>
       <c r="R34" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S34" s="11" t="s">
         <v>40</v>
@@ -4342,21 +4351,21 @@
         <v>42</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W34" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="30" customHeight="1">
       <c r="A35" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>24</v>
+      <c r="B35" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>26</v>
@@ -4368,10 +4377,10 @@
         <v>300</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>23</v>
@@ -4382,8 +4391,8 @@
       <c r="K35" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L35" s="7" t="s">
-        <v>295</v>
+      <c r="L35" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M35" s="8" t="s">
         <v>301</v>
@@ -4395,7 +4404,7 @@
         <v>66</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>302</v>
@@ -4413,21 +4422,21 @@
         <v>42</v>
       </c>
       <c r="V35" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W35" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:23" ht="30" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>303</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>24</v>
+      <c r="B36" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>26</v>
@@ -4439,10 +4448,10 @@
         <v>305</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>52</v>
@@ -4453,8 +4462,8 @@
       <c r="K36" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L36" s="11" t="s">
-        <v>295</v>
+      <c r="L36" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M36" s="12" t="s">
         <v>306</v>
@@ -4484,21 +4493,21 @@
         <v>42</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W36" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="30" customHeight="1">
       <c r="A37" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>24</v>
+      <c r="B37" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>26</v>
@@ -4510,10 +4519,10 @@
         <v>312</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>69</v>
@@ -4524,8 +4533,8 @@
       <c r="K37" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>288</v>
+      <c r="L37" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>313</v>
@@ -4555,21 +4564,21 @@
         <v>42</v>
       </c>
       <c r="V37" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W37" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:23" ht="30" customHeight="1">
       <c r="A38" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>24</v>
+      <c r="B38" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>26</v>
@@ -4581,10 +4590,10 @@
         <v>319</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I38" s="9" t="s">
         <v>69</v>
@@ -4595,8 +4604,8 @@
       <c r="K38" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L38" s="11" t="s">
-        <v>288</v>
+      <c r="L38" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M38" s="12" t="s">
         <v>320</v>
@@ -4626,21 +4635,21 @@
         <v>42</v>
       </c>
       <c r="V38" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W38" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="30" customHeight="1">
       <c r="A39" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
+      <c r="B39" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>26</v>
@@ -4652,10 +4661,10 @@
         <v>325</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>31</v>
@@ -4666,8 +4675,8 @@
       <c r="K39" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>288</v>
+      <c r="L39" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M39" s="8" t="s">
         <v>326</v>
@@ -4697,21 +4706,21 @@
         <v>42</v>
       </c>
       <c r="V39" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W39" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="30" customHeight="1">
       <c r="A40" s="9" t="s">
         <v>329</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>24</v>
+      <c r="B40" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>26</v>
@@ -4723,10 +4732,10 @@
         <v>331</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>31</v>
@@ -4737,8 +4746,8 @@
       <c r="K40" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L40" s="11" t="s">
-        <v>288</v>
+      <c r="L40" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M40" s="12" t="s">
         <v>313</v>
@@ -4768,21 +4777,21 @@
         <v>42</v>
       </c>
       <c r="V40" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W40" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="30" customHeight="1">
       <c r="A41" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
+      <c r="B41" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>26</v>
@@ -4794,10 +4803,10 @@
         <v>336</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>23</v>
@@ -4808,8 +4817,8 @@
       <c r="K41" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="L41" s="7" t="s">
-        <v>295</v>
+      <c r="L41" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="M41" s="8" t="s">
         <v>337</v>
@@ -4839,21 +4848,21 @@
         <v>42</v>
       </c>
       <c r="V41" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W41" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:23" ht="30" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>24</v>
+      <c r="B42" s="12" t="s">
+        <v>284</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>26</v>
@@ -4865,10 +4874,10 @@
         <v>342</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I42" s="9" t="s">
         <v>69</v>
@@ -4879,8 +4888,8 @@
       <c r="K42" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="L42" s="11" t="s">
-        <v>288</v>
+      <c r="L42" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="M42" s="12" t="s">
         <v>313</v>
@@ -4910,10 +4919,10 @@
         <v>42</v>
       </c>
       <c r="V42" s="11" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W42" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:23" ht="30" customHeight="1">
@@ -4969,13 +4978,13 @@
         <v>353</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S43" s="7" t="s">
         <v>40</v>
       </c>
       <c r="T43" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>42</v>
@@ -5031,7 +5040,7 @@
         <v>35</v>
       </c>
       <c r="O44" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P44" s="11" t="s">
         <v>364</v>
@@ -5040,7 +5049,7 @@
         <v>365</v>
       </c>
       <c r="R44" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S44" s="11" t="s">
         <v>40</v>
@@ -5099,7 +5108,7 @@
         <v>374</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O45" s="5" t="s">
         <v>36</v>
@@ -5111,7 +5120,7 @@
         <v>376</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S45" s="7" t="s">
         <v>40</v>
@@ -5123,33 +5132,33 @@
         <v>42</v>
       </c>
       <c r="V45" s="7" t="s">
-        <v>103</v>
+        <v>377</v>
       </c>
       <c r="W45" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:23" ht="30" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E46" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F46" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>379</v>
-      </c>
       <c r="G46" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H46" s="11" t="s">
         <v>372</v>
@@ -5164,10 +5173,10 @@
         <v>32</v>
       </c>
       <c r="L46" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M46" s="12" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N46" s="11" t="s">
         <v>48</v>
@@ -5176,10 +5185,10 @@
         <v>66</v>
       </c>
       <c r="P46" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q46" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="R46" s="11" t="s">
         <v>51</v>
@@ -5194,33 +5203,33 @@
         <v>42</v>
       </c>
       <c r="V46" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W46" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="47" spans="1:23" ht="45" customHeight="1">
       <c r="A47" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>109</v>
@@ -5235,10 +5244,10 @@
         <v>32</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>58</v>
@@ -5247,10 +5256,10 @@
         <v>66</v>
       </c>
       <c r="P47" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>77</v>
@@ -5265,33 +5274,33 @@
         <v>42</v>
       </c>
       <c r="V47" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="W47" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="48" spans="1:23" ht="30" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D48" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>404</v>
+      </c>
+      <c r="F48" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="E48" s="11" t="s">
-        <v>403</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>401</v>
-      </c>
       <c r="G48" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H48" s="11" t="s">
         <v>372</v>
@@ -5306,10 +5315,10 @@
         <v>32</v>
       </c>
       <c r="L48" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M48" s="12" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N48" s="11" t="s">
         <v>35</v>
@@ -5318,10 +5327,10 @@
         <v>66</v>
       </c>
       <c r="P48" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q48" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R48" s="11" t="s">
         <v>39</v>
@@ -5336,36 +5345,36 @@
         <v>42</v>
       </c>
       <c r="V48" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W48" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="49" spans="1:23" ht="30" customHeight="1">
       <c r="A49" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F49" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E49" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>411</v>
-      </c>
       <c r="G49" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>23</v>
@@ -5377,10 +5386,10 @@
         <v>32</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>48</v>
@@ -5389,10 +5398,10 @@
         <v>66</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R49" s="7" t="s">
         <v>39</v>
@@ -5407,33 +5416,33 @@
         <v>42</v>
       </c>
       <c r="V49" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W49" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:23" ht="30" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B50" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D50" s="11" t="s">
+        <v>424</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>425</v>
+      </c>
+      <c r="F50" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="E50" s="11" t="s">
-        <v>424</v>
-      </c>
-      <c r="F50" s="11" t="s">
-        <v>422</v>
-      </c>
       <c r="G50" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H50" s="11" t="s">
         <v>372</v>
@@ -5448,10 +5457,10 @@
         <v>32</v>
       </c>
       <c r="L50" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M50" s="12" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N50" s="11" t="s">
         <v>58</v>
@@ -5460,10 +5469,10 @@
         <v>66</v>
       </c>
       <c r="P50" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q50" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R50" s="11" t="s">
         <v>39</v>
@@ -5478,33 +5487,33 @@
         <v>42</v>
       </c>
       <c r="V50" s="11" t="s">
-        <v>102</v>
+        <v>431</v>
       </c>
       <c r="W50" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="51" spans="1:23" ht="30" customHeight="1">
       <c r="A51" s="5" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>109</v>
@@ -5519,10 +5528,10 @@
         <v>32</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M51" s="8" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N51" s="7" t="s">
         <v>35</v>
@@ -5531,10 +5540,10 @@
         <v>66</v>
       </c>
       <c r="P51" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>51</v>
@@ -5549,36 +5558,36 @@
         <v>42</v>
       </c>
       <c r="V51" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="W51" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="30" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E52" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="F52" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>442</v>
-      </c>
       <c r="G52" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>23</v>
@@ -5590,10 +5599,10 @@
         <v>32</v>
       </c>
       <c r="L52" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M52" s="12" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="N52" s="11" t="s">
         <v>35</v>
@@ -5602,13 +5611,13 @@
         <v>66</v>
       </c>
       <c r="P52" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q52" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="R52" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S52" s="11" t="s">
         <v>40</v>
@@ -5620,36 +5629,36 @@
         <v>42</v>
       </c>
       <c r="V52" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="W52" s="11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" spans="1:23" ht="30" customHeight="1">
       <c r="A53" s="5" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E53" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="F53" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>454</v>
-      </c>
       <c r="G53" s="7" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>23</v>
@@ -5661,10 +5670,10 @@
         <v>32</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N53" s="7" t="s">
         <v>48</v>
@@ -5673,10 +5682,10 @@
         <v>66</v>
       </c>
       <c r="P53" s="7" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>39</v>
@@ -5691,36 +5700,36 @@
         <v>42</v>
       </c>
       <c r="V53" s="7" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="W53" s="7" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="54" spans="1:23" ht="30" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>23</v>
@@ -5732,10 +5741,10 @@
         <v>32</v>
       </c>
       <c r="L54" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="M54" s="12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="N54" s="11" t="s">
         <v>48</v>
@@ -5744,10 +5753,10 @@
         <v>66</v>
       </c>
       <c r="P54" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Q54" s="11" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="R54" s="11" t="s">
         <v>77</v>
@@ -5762,33 +5771,33 @@
         <v>42</v>
       </c>
       <c r="V54" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="W54" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:23" ht="30" customHeight="1">
       <c r="A55" s="5" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D55" s="7" t="s">
         <v>106</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>109</v>
@@ -5803,10 +5812,10 @@
         <v>32</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N55" s="7" t="s">
         <v>35</v>
@@ -5815,10 +5824,10 @@
         <v>66</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="R55" s="7" t="s">
         <v>51</v>
@@ -5833,33 +5842,33 @@
         <v>42</v>
       </c>
       <c r="V55" s="7" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="W55" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="56" spans="1:23" ht="30" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>106</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H56" s="11" t="s">
         <v>109</v>
@@ -5874,10 +5883,10 @@
         <v>32</v>
       </c>
       <c r="L56" s="11" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="M56" s="12" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="N56" s="11" t="s">
         <v>35</v>
@@ -5886,10 +5895,10 @@
         <v>66</v>
       </c>
       <c r="P56" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="Q56" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="R56" s="11" t="s">
         <v>51</v>
@@ -5904,36 +5913,36 @@
         <v>42</v>
       </c>
       <c r="V56" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="W56" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="57" spans="1:23" ht="30" customHeight="1">
       <c r="A57" s="5" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B57" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H57" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>23</v>
@@ -5945,10 +5954,10 @@
         <v>32</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="N57" s="7" t="s">
         <v>48</v>
@@ -5957,10 +5966,10 @@
         <v>66</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="R57" s="7" t="s">
         <v>77</v>
@@ -5975,10 +5984,10 @@
         <v>42</v>
       </c>
       <c r="V57" s="7" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="W57" s="7" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>
@@ -5997,7 +6006,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="45.7109375" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="18.7109375" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" customWidth="1"/>
@@ -6023,7 +6032,7 @@
   <sheetData>
     <row r="1" spans="1:23" ht="32" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -6048,13 +6057,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="C2" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F2" s="3">
         <v>55</v>
@@ -6062,41 +6071,41 @@
     </row>
     <row r="3" spans="1:23">
       <c r="C3" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="C4" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:23">
       <c r="C5" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -6104,13 +6113,13 @@
     </row>
     <row r="6" spans="1:23">
       <c r="C6" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F6" s="3">
         <v>128</v>
@@ -6195,19 +6204,19 @@
         <v>24</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>109</v>
@@ -6216,16 +6225,16 @@
         <v>23</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>58</v>
@@ -6234,10 +6243,10 @@
         <v>66</v>
       </c>
       <c r="P9" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="R9" s="7" t="s">
         <v>39</v>
@@ -6246,39 +6255,39 @@
         <v>40</v>
       </c>
       <c r="T9" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U9" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V9" s="7" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="W9" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="30" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>24</v>
+      <c r="B10" s="12" t="s">
+        <v>539</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="H10" s="11" t="s">
         <v>109</v>
@@ -6287,16 +6296,16 @@
         <v>31</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N10" s="11" t="s">
         <v>35</v>
@@ -6305,10 +6314,10 @@
         <v>36</v>
       </c>
       <c r="P10" s="11" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="Q10" s="11" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="R10" s="11" t="s">
         <v>39</v>
@@ -6317,16 +6326,16 @@
         <v>40</v>
       </c>
       <c r="T10" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V10" s="11" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="W10" s="11" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -6337,34 +6346,34 @@
         <v>24</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>31</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>24</v>
@@ -6376,10 +6385,10 @@
         <v>36</v>
       </c>
       <c r="P11" s="7" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>51</v>
@@ -6388,16 +6397,16 @@
         <v>40</v>
       </c>
       <c r="T11" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U11" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V11" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="30" customHeight="1">
@@ -6408,37 +6417,37 @@
         <v>24</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K12" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="N12" s="11" t="s">
         <v>35</v>
@@ -6447,66 +6456,66 @@
         <v>36</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="Q12" s="11" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="R12" s="11" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="T12" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V12" s="11" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
+      <c r="B13" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I13" s="5" t="s">
         <v>23</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>24</v>
@@ -6518,13 +6527,13 @@
         <v>66</v>
       </c>
       <c r="P13" s="7" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>115</v>
+        <v>205</v>
       </c>
       <c r="S13" s="7" t="s">
         <v>40</v>
@@ -6533,13 +6542,13 @@
         <v>41</v>
       </c>
       <c r="U13" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V13" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="W13" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="30" customHeight="1">
@@ -6556,31 +6565,31 @@
         <v>358</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>31</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K14" s="9" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="N14" s="11" t="s">
         <v>35</v>
@@ -6589,10 +6598,10 @@
         <v>36</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="Q14" s="11" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="R14" s="11" t="s">
         <v>51</v>
@@ -6604,13 +6613,13 @@
         <v>41</v>
       </c>
       <c r="U14" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V14" s="11" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>
@@ -6633,27 +6642,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="7" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="8" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="6" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
